--- a/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
+++ b/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
@@ -1,92 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Sensitivity analyses/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1481427-6368-714C-ADE1-7BEB099304D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="20">
-  <si>
-    <t>analysis</t>
-  </si>
-  <si>
-    <t>disease</t>
-  </si>
-  <si>
-    <t>tot_daly</t>
-  </si>
-  <si>
-    <t>tot_daly_low</t>
-  </si>
-  <si>
-    <t>tot_daly_up</t>
-  </si>
-  <si>
-    <t>relative_perc_daly</t>
-  </si>
-  <si>
-    <t>outcome</t>
-  </si>
-  <si>
-    <t>main</t>
-  </si>
-  <si>
-    <t>mort</t>
-  </si>
-  <si>
-    <t>cvd</t>
-  </si>
-  <si>
-    <t>cancer</t>
-  </si>
-  <si>
-    <t>diab2</t>
-  </si>
-  <si>
-    <t>dem</t>
-  </si>
-  <si>
-    <t>dep</t>
-  </si>
-  <si>
-    <t>All</t>
-  </si>
-  <si>
-    <t>sc1</t>
-  </si>
-  <si>
-    <t>bc</t>
-  </si>
-  <si>
-    <t>cc</t>
-  </si>
-  <si>
-    <t>sc2</t>
-  </si>
-  <si>
-    <t>sc3</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -134,21 +63,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -186,7 +107,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -220,7 +141,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -255,10 +175,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -431,402 +350,511 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.1640625" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>analysis</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_low</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>tot_daly_up</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>relative_perc_daly</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="C2">
-        <v>604884.65800000005</v>
+        <v>604884.6580000001</v>
       </c>
       <c r="D2">
-        <v>587117.32299999997</v>
+        <v>587117.323</v>
       </c>
       <c r="E2">
-        <v>622704.42599999998</v>
-      </c>
-      <c r="G2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
+        <v>622704.426</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="C3">
         <v>35940.072</v>
       </c>
       <c r="D3">
-        <v>34538.406999999999</v>
+        <v>34538.407</v>
       </c>
       <c r="E3">
         <v>37361.195</v>
       </c>
-      <c r="G3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" t="s">
-        <v>10</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>cancer</t>
+        </is>
       </c>
       <c r="C4">
-        <v>47085.235999999997</v>
+        <v>47085.236</v>
       </c>
       <c r="D4">
-        <v>44414.474999999999</v>
+        <v>44414.475</v>
       </c>
       <c r="E4">
-        <v>49916.631000000001</v>
-      </c>
-      <c r="G4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" t="s">
-        <v>11</v>
+        <v>49916.631</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="C5">
-        <v>12502.744000000001</v>
+        <v>12502.744</v>
       </c>
       <c r="D5">
-        <v>11875.522000000001</v>
+        <v>11875.522</v>
       </c>
       <c r="E5">
         <v>13142.02</v>
       </c>
-      <c r="G5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="C6">
-        <v>23252.173999999999</v>
+        <v>23252.174</v>
       </c>
       <c r="D6">
         <v>22102.18</v>
       </c>
       <c r="E6">
-        <v>24412.370999999999</v>
-      </c>
-      <c r="G6" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
+        <v>24412.371</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="C7">
-        <v>41027.608999999997</v>
+        <v>41027.609</v>
       </c>
       <c r="D7">
-        <v>38919.728000000003</v>
+        <v>38919.728</v>
       </c>
       <c r="E7">
         <v>43216.125</v>
       </c>
-      <c r="G7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>main</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C8">
-        <v>764692.49300000002</v>
+        <v>764692.493</v>
       </c>
       <c r="D8">
-        <v>738967.63500000001</v>
+        <v>738967.635</v>
       </c>
       <c r="E8">
-        <v>790752.76800000004</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>8</v>
+        <v>790752.768</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>mort</t>
+        </is>
       </c>
       <c r="C9">
-        <v>202863.99600000001</v>
+        <v>202863.996</v>
       </c>
       <c r="D9">
-        <v>196543.07199999999</v>
+        <v>196543.072</v>
       </c>
       <c r="E9">
-        <v>209209.69399999999</v>
+        <v>209209.694</v>
       </c>
       <c r="F9">
-        <v>-66.462367111317946</v>
-      </c>
-      <c r="G9" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
+        <v>-66.46236711131795</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>bc</t>
+        </is>
       </c>
       <c r="C10">
-        <v>4318.0250000000005</v>
+        <v>4318.133</v>
       </c>
       <c r="D10">
-        <v>3973.0829999999992</v>
+        <v>3970.713</v>
       </c>
       <c r="E10">
-        <v>4685.4610000000002</v>
-      </c>
-      <c r="G10" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
+        <v>4686.567</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>cc</t>
+        </is>
       </c>
       <c r="C11">
-        <v>2635.237000000001</v>
+        <v>2635.507000000001</v>
       </c>
       <c r="D11">
-        <v>2525.373000000001</v>
+        <v>2524.905</v>
       </c>
       <c r="E11">
-        <v>2750.0390000000002</v>
-      </c>
-      <c r="G11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>9</v>
+        <v>2750.237</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>cvd</t>
+        </is>
       </c>
       <c r="C12">
-        <v>36614.697999999997</v>
+        <v>36619.72099999999</v>
       </c>
       <c r="D12">
-        <v>35353.686000000002</v>
+        <v>35349.97199999999</v>
       </c>
       <c r="E12">
-        <v>37888.324000000001</v>
+        <v>37897.425</v>
       </c>
       <c r="F12">
-        <v>1.8770858333283149</v>
-      </c>
-      <c r="G12" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>11</v>
+        <v>1.891061876559375</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>diab2</t>
+        </is>
       </c>
       <c r="C13">
-        <v>26078.447</v>
+        <v>26079.172</v>
       </c>
       <c r="D13">
-        <v>25294.498</v>
+        <v>25300.53999999999</v>
       </c>
       <c r="E13">
-        <v>26874.687000000002</v>
+        <v>26868.49799999999</v>
       </c>
       <c r="F13">
-        <v>108.5817881258706</v>
-      </c>
-      <c r="G13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>12</v>
+        <v>108.587586852934</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>dem</t>
+        </is>
       </c>
       <c r="C14">
-        <v>11722.369000000001</v>
+        <v>11721.661</v>
       </c>
       <c r="D14">
-        <v>11175.915000000001</v>
+        <v>11178.246</v>
       </c>
       <c r="E14">
-        <v>12279.226000000001</v>
+        <v>12280.096</v>
       </c>
       <c r="F14">
-        <v>-49.585922589431853</v>
-      </c>
-      <c r="G14" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>13</v>
+        <v>-49.58896746600984</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>dep</t>
+        </is>
       </c>
       <c r="C15">
-        <v>77759.21100000001</v>
+        <v>72400.62299999999</v>
       </c>
       <c r="D15">
-        <v>74882.989000000001</v>
+        <v>69674.46400000001</v>
       </c>
       <c r="E15">
-        <v>80671.297999999981</v>
+        <v>75196.823</v>
       </c>
       <c r="F15">
-        <v>89.528985225534385</v>
-      </c>
-      <c r="G15" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>14</v>
+        <v>76.46805350026612</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sc1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C16">
-        <v>361991.98300000001</v>
+        <v>356638.813</v>
       </c>
       <c r="D16">
-        <v>349748.61599999998</v>
+        <v>344541.9119999999</v>
       </c>
       <c r="E16">
-        <v>374358.72899999988</v>
+        <v>368889.34</v>
       </c>
       <c r="F16">
-        <v>-52.661757985899307</v>
-      </c>
-      <c r="G16" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17" t="s">
-        <v>14</v>
+        <v>-53.36180016612246</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sc2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C17">
         <v>741009.755</v>
       </c>
       <c r="D17">
-        <v>717338.65500000003</v>
+        <v>717338.655</v>
       </c>
       <c r="E17">
-        <v>764807.04400000011</v>
+        <v>764807.0440000001</v>
       </c>
       <c r="F17">
         <v>-3.097027657102946</v>
       </c>
-      <c r="G17" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" t="s">
-        <v>14</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sc3</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
       </c>
       <c r="C18">
-        <v>650563.98200000008</v>
+        <v>650563.9820000001</v>
       </c>
       <c r="D18">
-        <v>628286.04099999997</v>
+        <v>628286.041</v>
       </c>
       <c r="E18">
-        <v>673019.32899999991</v>
+        <v>673019.3289999999</v>
       </c>
       <c r="F18">
-        <v>-14.924758912207601</v>
-      </c>
-      <c r="G18" t="s">
-        <v>2</v>
+        <v>-14.9247589122076</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>tot_daly</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
+++ b/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
@@ -411,6 +411,9 @@
       <c r="E2">
         <v>622704.426</v>
       </c>
+      <c r="F2">
+        <v>-41.04019530282086</v>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>tot_daly</t>
@@ -437,6 +440,9 @@
       <c r="E3">
         <v>37361.195</v>
       </c>
+      <c r="F3">
+        <v>892.3152435532128</v>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>tot_daly</t>
@@ -463,6 +469,9 @@
       <c r="E4">
         <v>49916.631</v>
       </c>
+      <c r="F4">
+        <v>657.4323573529504</v>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>tot_daly</t>
@@ -489,6 +498,9 @@
       <c r="E5">
         <v>13142.02</v>
       </c>
+      <c r="F5">
+        <v>2752.484326640616</v>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>tot_daly</t>
@@ -515,6 +527,9 @@
       <c r="E6">
         <v>24412.371</v>
       </c>
+      <c r="F6">
+        <v>1433.786961167588</v>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>tot_daly</t>
@@ -541,6 +556,9 @@
       <c r="E7">
         <v>43216.125</v>
       </c>
+      <c r="F7">
+        <v>769.265408569142</v>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>tot_daly</t>
@@ -566,6 +584,9 @@
       </c>
       <c r="E8">
         <v>790752.768</v>
+      </c>
+      <c r="F8">
+        <v>-53.36180016612246</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>

--- a/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
+++ b/output/Tables/Sensitivity analyses/sensitivity_analysis.xlsx
@@ -412,7 +412,7 @@
         <v>622704.426</v>
       </c>
       <c r="F2">
-        <v>-41.04019530282086</v>
+        <v>198.1725046962005</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -441,7 +441,7 @@
         <v>37361.195</v>
       </c>
       <c r="F3">
-        <v>892.3152435532128</v>
+        <v>-1.855964440581048</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -469,9 +469,6 @@
       <c r="E4">
         <v>49916.631</v>
       </c>
-      <c r="F4">
-        <v>657.4323573529504</v>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>tot_daly</t>
@@ -499,7 +496,7 @@
         <v>13142.02</v>
       </c>
       <c r="F5">
-        <v>2752.484326640616</v>
+        <v>-52.05850860602476</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -528,7 +525,7 @@
         <v>24412.371</v>
       </c>
       <c r="F6">
-        <v>1433.786961167588</v>
+        <v>98.36927548066778</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -557,7 +554,7 @@
         <v>43216.125</v>
       </c>
       <c r="F7">
-        <v>769.265408569142</v>
+        <v>-43.33251939006104</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -586,7 +583,7 @@
         <v>790752.768</v>
       </c>
       <c r="F8">
-        <v>-53.36180016612246</v>
+        <v>114.41650911955</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
